--- a/stores picture/雄仔廚房.xlsx
+++ b/stores picture/雄仔廚房.xlsx
@@ -16,22 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>高麗菜水餃 (每顆)</t>
-  </si>
-  <si>
-    <t>韭菜水餃 (每顆)</t>
-  </si>
-  <si>
-    <t>玉米水餃 (每顆)</t>
-  </si>
-  <si>
-    <t>泡菜水餃 (每顆)</t>
-  </si>
-  <si>
-    <t>剝皮辣椒水餃 (每顆)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>丸子湯</t>
   </si>
@@ -81,31 +66,97 @@
     <t>椒鹽雞丁炒飯</t>
   </si>
   <si>
-    <t>泡菜燒肉飯</t>
-  </si>
-  <si>
-    <t>咖哩豬排飯</t>
-  </si>
-  <si>
-    <t>咖哩雞排飯</t>
-  </si>
-  <si>
-    <t>炸豬排飯</t>
-  </si>
-  <si>
-    <t>炸雞排飯</t>
-  </si>
-  <si>
-    <t>椒鹽雞丁飯</t>
-  </si>
-  <si>
-    <t>限量爌肉飯</t>
-  </si>
-  <si>
-    <t>香煎鯖魚飯</t>
-  </si>
-  <si>
-    <t>打拋豬飯</t>
+    <t>韭菜手工大水餃 (1顆)</t>
+  </si>
+  <si>
+    <t>玉米手工大水餃 (1顆)</t>
+  </si>
+  <si>
+    <t>高麗菜手工大水餃 (1顆)</t>
+  </si>
+  <si>
+    <t>泡菜手工大水餃 (1顆)</t>
+  </si>
+  <si>
+    <t>剝皮辣椒手工大水餃 (1顆)</t>
+  </si>
+  <si>
+    <t>荷包蛋 (單點)</t>
+  </si>
+  <si>
+    <t>綜合丸子湯</t>
+  </si>
+  <si>
+    <t>打拋豬飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>泡菜燒肉飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>炸豬排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>咖哩豬排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>炸雞排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>咖哩雞排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>炸蝦排 (單點)</t>
+  </si>
+  <si>
+    <t>炸蝦排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>炸蝦排炒飯</t>
+  </si>
+  <si>
+    <t>炸雞腿 (單點)</t>
+  </si>
+  <si>
+    <t>炸雞腿飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>炸雞腿炒飯</t>
+  </si>
+  <si>
+    <t>椒鹽雞丁飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>限量爌肉飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>香煎鯖魚飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>秘製燒肉 (單點)</t>
+  </si>
+  <si>
+    <t>秘製燒肉飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>秘製燒肉炒飯</t>
+  </si>
+  <si>
+    <t>起司豬排 (單點)</t>
+  </si>
+  <si>
+    <t>起司豬排飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>起司豬排炒飯</t>
+  </si>
+  <si>
+    <t>黃金大腿 (單點)</t>
+  </si>
+  <si>
+    <t>黃金大腿飯 (盒飯)</t>
+  </si>
+  <si>
+    <t>黃金大腿炒飯</t>
   </si>
 </sst>
 </file>
@@ -475,15 +526,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.453125" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>10</v>
@@ -491,55 +543,55 @@
     </row>
     <row r="2" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B7" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" s="1">
         <v>30</v>
@@ -547,87 +599,87 @@
     </row>
     <row r="9" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="B14" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B18" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1">
         <v>100</v>
@@ -635,31 +687,31 @@
     </row>
     <row r="20" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B23" s="1">
         <v>100</v>
@@ -667,31 +719,31 @@
     </row>
     <row r="24" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1">
         <v>100</v>
@@ -699,7 +751,7 @@
     </row>
     <row r="28" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1">
         <v>100</v>
@@ -707,18 +759,154 @@
     </row>
     <row r="29" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B29" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B30" s="1">
         <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
